--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="service_charge_basic_info" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="118">
   <si>
     <t>TC ID</t>
   </si>
@@ -161,8 +162,9 @@
 |---|------|-----------------|
 | 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
 | 2 | Click the percentage input for Audio Conferencing and clear the value | The field is empty |
-| 3 | Type -0.01 and move focus away by pressing Tab | NEEDS-LIVE-CONFIRM: whether the field rejects the value (announced: is invalid or visible error message) and whether Tab successfully moves focus out of the field (escapable by Tab or click) |
-"Notes": BVA min-1 case. The test requires both: an announced rejection signal and that Tab or click successfully moves focus out of the field. A silent rejection or a focus trap is a defect.
+| 3 | Type -0.01 while the field remains focused | The value remains in the field and the field is marked invalid while focused with is invalid |
+| 4 | Press Tab to move focus away and observe the Save button | After focus leaves, the app may restore the stored value and clear the invalid marking; Save remains disabled |
+"Notes": BVA min-1 case. Observed live: the rejection marking is reliable while focused, may clear after blur, and Save remains disabled after blur.
 ---</t>
   </si>
   <si>
@@ -177,8 +179,9 @@
 |---|------|-----------------|
 | 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
 | 2 | Click the percentage input for Audio Conferencing and clear the value | The field is empty |
-| 3 | Type 100.01 and move focus away by pressing Tab | NEEDS-LIVE-CONFIRM: whether the field rejects the value (is invalid announced, focus movable by Tab or click) or accepts it |
-"Notes": BVA max+1 case. Both an announced rejection signal and the ability to move focus out of the field are required.
+| 3 | Type 100.01 while the field remains focused | The value remains in the field and the field is marked invalid while focused with is invalid |
+| 4 | Press Tab to move focus away and observe the Save button | After focus leaves, the app may restore the stored value and clear the invalid marking; Save remains disabled |
+"Notes": BVA max+1 case. Observed live: the rejection marking is reliable while focused, may clear after blur, and Save remains disabled after blur.
 ---</t>
   </si>
   <si>
@@ -217,23 +220,24 @@
     <t>TC-SVC-BAS-009</t>
   </si>
   <si>
-    <t>Entering alphabetic text into a percentage field</t>
+    <t>Entering alphabetic text into a percentage field is flagged while focused</t>
   </si>
   <si>
     <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
 | # | Step | Expected Result |
 |---|------|-----------------|
 | 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Click the percentage input for APP Downloaded and type abc | The characters appear in the field - inputmode="decimal" does not block entry |
-| 3 | Move focus away by pressing Tab | is invalid is set on the field and Save is disabled; no error message text is rendered |
-"Notes": Negative case. Observed live: alpha input is not blocked at entry; validation error is the only rejection signal on blur.
+| 2 | Click the row-0 percentage field for App Quality Assurance and type abc | The letters are accepted into the field |
+| 3 | While the field is still focused, observe its invalid state | The field is flagged invalid while focused: is invalid, red border, and error icon are shown |
+| 4 | Press Tab to move focus away and observe the Save button | After focus moves away, the app may restore the stored value and clear the invalid flag; Save remains disabled throughout |
+"Notes": Negative case. Observed live: alpha input is accepted at entry, invalid while focused, and may be restored after blur; Save remains disabled.
 ---</t>
   </si>
   <si>
     <t>TC-SVC-BAS-010</t>
   </si>
   <si>
-    <t>Entering a malformed decimal value</t>
+    <t>Entering a malformed decimal value is flagged while focused</t>
   </si>
   <si>
     <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
@@ -241,8 +245,9 @@
 |---|------|-----------------|
 | 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
 | 2 | Click the percentage input for Audio Conferencing and type 1.2.3 | The string appears verbatim in the field |
-| 3 | Move focus away by pressing Tab | is invalid is set and Save is disabled; no error message text is rendered |
-"Notes": Negative case - malformed decimal. Observed live: "1.2.3" is kept verbatim in input.value; the validator rejects it silently via validation error only.
+| 3 | While the field is still focused, observe its invalid state | The string remains verbatim in the field and the field is marked invalid while focused with is invalid |
+| 4 | Press Tab to move focus away and observe the Save button | After focus leaves, the app may restore the stored value and clear the invalid marking; Save remains disabled |
+"Notes": Negative case - malformed decimal. Observed live: 1.2.3 is kept verbatim and marked invalid while focused; after blur, Save remains disabled.
 ---</t>
   </si>
   <si>
@@ -256,9 +261,10 @@
 | # | Step | Expected Result |
 |---|------|-----------------|
 | 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Click the percentage input for Audio Conferencing and type -5 | The value appears or the browser prevents the minus sign |
-| 3 | Move focus away by pressing Tab | NEEDS-LIVE-CONFIRM: whether a rejection signal appears (is invalid, escapable by Tab or click) or the value is silently accepted |
-"Notes": Negative case - sign constraint. Both an announced rejection signal and the ability to move focus out of the field are required.
+| 2 | Click the percentage input for Audio Conferencing and type -5 | The value remains in the field |
+| 3 | While the field is still focused, observe its invalid state | The field is marked invalid while focused with is invalid |
+| 4 | Press Tab to move focus away and observe the Save button | After focus leaves, the app may restore the stored value and clear the invalid marking; Save remains disabled |
+"Notes": Negative case - sign constraint. Observed live: the rejection marking is reliable while focused, may clear after blur, and Save remains disabled after blur.
 ---</t>
   </si>
   <si>
@@ -336,9 +342,10 @@
 | # | Step | Expected Result |
 |---|------|-----------------|
 | 1 | Navigate to the Basic Information tab | The tab loads |
-| 2 | Click the APP Downloaded percentage input, clear it, and paste a 50-digit numeric string (12345678901234567890123456789012345678901234567890) | The full string appears in the field without truncation |
-| 3 | Move focus away | is invalid is set and Save is disabled - the validator rejects the out-of-range value |
-"Notes": Very long input case. Observed live: no truncation; field accepts the full string; validator rejects via validation error only.
+| 2 | Click the APP Downloaded percentage input, clear it, and paste a 50-digit numeric string (12345678901234567890123456789012345678901234567890) | The full 50-digit string stays in the field verbatim while focused |
+| 3 | While the field is still focused, observe its invalid state | The field is marked invalid while focused with is invalid |
+| 4 | Press Tab to move focus away and observe the Save button | After focus leaves, the app may restore the stored value and clear the invalid marking; Save remains disabled |
+"Notes": Very long input case. Observed live: no truncation or scientific-notation conversion while focused; the field keeps the full string verbatim, marks it invalid while focused, and Save remains disabled after blur.
 ---</t>
   </si>
   <si>
@@ -437,9 +444,9 @@
 |---|------|-----------------|
 | 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
 | 2 | Edit any percentage field so that Save enables | Save is enabled (form is dirty) |
-| 3 | Click a navigation element to leave the page (e.g. open a different Settings tab or the top nav) | NEEDS-LIVE-CONFIRM: whether an "Unsaved changes" alert dialog appears. If so, confirm the dialog's testid ( default: dlgSaveChanges / "Save Changes Confirm" button, unless MCP walk proves otherwise) |
-| 4 | If a dialog appears: click the confirm/discard action | The navigation proceeds and unsaved edits are discarded |
-"Notes": State-transition Dirty -&gt; Navigate-Away-Prompt. NEEDS-LIVE-CONFIRM: if no dialog appears, classify that as a potential defect and escalate.
+| 3 | Press the browser Back button | The browser's native leave-page dialog appears (type: beforeunload). Browser-back triggers the browser's native dialog; in-app tab navigation shows the application's "Unsaved changes" modal (Stay / Discard). Both behaviours were confirmed on the live site. |
+| 4 | Dismiss the dialog (stay on page) | Navigation is cancelled; the page remains open with the edit still present. Reload or discard the edit to restore clean state. |
+"Notes": Browser-back fires the browser's native beforeunload dialog. In-app tab navigation (e.g. clicking the History tab) shows the application's own "Unsaved changes" modal instead - that path is covered by TC-SVC-HIS-014.
 ---</t>
   </si>
   <si>
@@ -586,7 +593,10 @@
     <t>Pass:30 Fail:0 Skipped:0 Blocked:0</t>
   </si>
   <si>
-    <t>Last Updated: 2026-08-11</t>
+    <t>Last Updated: 2026-08-14</t>
+  </si>
+  <si>
+    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
   </si>
 </sst>
 </file>
@@ -2308,4 +2318,20 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -593,10 +593,10 @@
     <t>Pass:30 Fail:0 Skipped:0 Blocked:0</t>
   </si>
   <si>
-    <t>Last Updated: 2026-08-14</t>
-  </si>
-  <si>
-    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
+    <t>Last Updated: 2026-08-15</t>
+  </si>
+  <si>
+    <t>6729770ff2e77acf7dfad5e1019f025e9612e9fa3d5a8ea5b9a5f4adb8ffb470</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="231">
   <si>
     <t>TC ID</t>
   </si>
@@ -82,38 +82,58 @@
     <t>Pass</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604 and the page is in its default state.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Service Charge page on the Basic Information tab | The tab loads and 79 rows are visible |
-| 2 | Click the percentage input for Audio Conferencing (service-charge-percentage-8, default 24.00 %) and clear the value | The field is empty and focus is in the field |
-| 3 | Type 50.00 into the field and move focus away | The field retains 50.00 and Save becomes enabled |
-| 4 | Restore: clear the field, type 24.00, and save | The field reverts to 24.00 % and Save becomes disabled after reload |
-"Notes": Positive mid-range case. Confirms the field accepts a valid decimal value and that Save enables on any edit.
----</t>
-  </si>
-  <si>
-    <t>1. (no steps defined)</t>
+    <t>The Service Charge Basic Information page is open for office 1604 and the page is in its default state</t>
+  </si>
+  <si>
+    <t>1. Navigate to Location Settings for office 1604 and open the Service Charge page on the Basic Information tab</t>
+  </si>
+  <si>
+    <t>The tab loads and 79 rows are visible</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>2. Click the percentage input for Audio Conferencing (service-charge-percentage-8, default 24.00 %) and clear the value</t>
+  </si>
+  <si>
+    <t>The field is empty and focus is in the field</t>
+  </si>
+  <si>
+    <t>3. Type 50.00 into the field and move focus away</t>
+  </si>
+  <si>
+    <t>The field retains `50.00` and Save becomes enabled</t>
+  </si>
+  <si>
+    <t>4. Restore: clear the field, type 24.00, and save</t>
+  </si>
+  <si>
+    <t>The field reverts to `24.00 %` and Save becomes disabled after reload</t>
+  </si>
+  <si>
     <t>TC-SVC-BAS-002</t>
   </si>
   <si>
     <t>Editing a percentage field to 0.00 is accepted and enables Save</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604 with the Audio Conferencing row showing 24.00 %.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Service Charge page on the Basic Information tab | The tab loads and 79 rows are visible |
-| 2 | Click the percentage input for Audio Conferencing and clear the value | The field is empty |
-| 3 | Type 0.00 and move focus away | The field retains 0.00 and Save becomes enabled |
-| 4 | Restore: clear the field, type 24.00, and save | The field is restored to 24.00 % |
-"Notes": Minimum boundary positive case. 0.00 is a valid entry (row 0 defaults to 0.00 %).
----</t>
+    <t>The Service Charge Basic Information page is open for office 1604 with the Audio Conferencing row showing 24.00 %</t>
+  </si>
+  <si>
+    <t>2. Click the percentage input for Audio Conferencing and clear the value</t>
+  </si>
+  <si>
+    <t>The field is empty</t>
+  </si>
+  <si>
+    <t>3. Type 0.00 and move focus away</t>
+  </si>
+  <si>
+    <t>The field retains `0.00` and Save becomes enabled</t>
+  </si>
+  <si>
+    <t>The field is restored to `24.00 %`</t>
   </si>
   <si>
     <t>TC-SVC-BAS-003</t>
@@ -122,15 +142,22 @@
     <t>Editing a percentage field to 100.00</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Service Charge page on the Basic Information tab | The tab loads |
-| 2 | Click the percentage input for Audio Conferencing and clear the value | The field is empty |
-| 3 | Type 100.00 and move focus away | The field accepts the value: input.value shows "100.00 %", validation error is absent, and Save becomes enabled |
-| 4 | Restore: return the field to its original value and save | The field is restored |
-"Notes": Maximum boundary case. Observed live: 100.00 is accepted without restriction - no cap enforced at 100.
----</t>
+    <t>The Service Charge Basic Information page is open for office 1604</t>
+  </si>
+  <si>
+    <t>The tab loads</t>
+  </si>
+  <si>
+    <t>3. Type 100.00 and move focus away</t>
+  </si>
+  <si>
+    <t>The field accepts the value: input.value shows "100.00 %", `aria-invalid` is absent, and Save becomes enabled</t>
+  </si>
+  <si>
+    <t>4. Restore: return the field to its original value and save</t>
+  </si>
+  <si>
+    <t>The field is restored</t>
   </si>
   <si>
     <t>TC-SVC-BAS-004</t>
@@ -139,16 +166,28 @@
     <t>Saved percentage value persists after page reload</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604 and the Audio Conferencing percentage (service-charge-percentage-8) has its default value 24.00 %.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Service Charge page on the Basic Information tab | The tab loads |
-| 2 | Click the percentage input for Audio Conferencing, clear it, and type 30.00 | The field shows 30.00 and Save is enabled |
-| 3 | Click Save | Save completes without error |
-| 4 | Reload the page and re-open the Basic Information tab | The Audio Conferencing percentage reads 30.00 % |
-| 5 | Restore: click the field, clear it, type 24.00, click Save, and reload | The field is restored to 24.00 % |
-"Notes": Persistence verification via reload and DOM read. Confirms the value was actually persisted server-side, not just held in local state.
----</t>
+    <t>The Service Charge Basic Information page is open for office 1604 and the Audio Conferencing percentage (service-charge-percentage-8) has its default value 24.00 %</t>
+  </si>
+  <si>
+    <t>2. Click the percentage input for Audio Conferencing, clear it, and type 30.00</t>
+  </si>
+  <si>
+    <t>The field shows `30.00` and Save is enabled</t>
+  </si>
+  <si>
+    <t>3. Click Save</t>
+  </si>
+  <si>
+    <t>Save completes without error</t>
+  </si>
+  <si>
+    <t>4. Reload the page and re-open the Basic Information tab</t>
+  </si>
+  <si>
+    <t>The Audio Conferencing percentage reads `30.00 %`</t>
+  </si>
+  <si>
+    <t>5. Restore: click the field, clear it, type 24.00, click Save, and reload</t>
   </si>
   <si>
     <t>TC-SVC-BAS-005</t>
@@ -157,15 +196,19 @@
     <t>Entering a value just below zero (negative boundary)</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Click the percentage input for Audio Conferencing and clear the value | The field is empty |
-| 3 | Type -0.01 while the field remains focused | The value remains in the field and the field is marked invalid while focused with is invalid |
-| 4 | Press Tab to move focus away and observe the Save button | After focus leaves, the app may restore the stored value and clear the invalid marking; Save remains disabled |
-"Notes": BVA min-1 case. Observed live: the rejection marking is reliable while focused, may clear after blur, and Save remains disabled after blur.
----</t>
+    <t>1. Navigate to Location Settings for office 1604 and open the Basic Information tab</t>
+  </si>
+  <si>
+    <t>3. Type -0.01 while the field remains focused</t>
+  </si>
+  <si>
+    <t>The value remains in the field and the field is marked invalid while focused with `aria-invalid="true"`</t>
+  </si>
+  <si>
+    <t>4. Press Tab to move focus away and observe the Save button</t>
+  </si>
+  <si>
+    <t>After focus leaves, the app may restore the stored value and clear the invalid marking; Save remains disabled</t>
   </si>
   <si>
     <t>TC-SVC-BAS-006</t>
@@ -174,15 +217,7 @@
     <t>Entering a value just above 100</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Click the percentage input for Audio Conferencing and clear the value | The field is empty |
-| 3 | Type 100.01 while the field remains focused | The value remains in the field and the field is marked invalid while focused with is invalid |
-| 4 | Press Tab to move focus away and observe the Save button | After focus leaves, the app may restore the stored value and clear the invalid marking; Save remains disabled |
-"Notes": BVA max+1 case. Observed live: the rejection marking is reliable while focused, may clear after blur, and Save remains disabled after blur.
----</t>
+    <t>3. Type 100.01 while the field remains focused</t>
   </si>
   <si>
     <t>TC-SVC-BAS-007</t>
@@ -191,14 +226,10 @@
     <t>Entering a value with three decimal places</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Click the percentage input for Audio Conferencing and clear the value | The field is empty |
-| 3 | Type 24.005 and move focus away | The value is silently rounded to "24.00 %" - the third decimal is discarded; validation error is absent |
-"Notes": Decimal-step boundary case. Observed live: the application rounds silently to two decimal places without any rejection signal.
----</t>
+    <t>3. Type 24.005 and move focus away</t>
+  </si>
+  <si>
+    <t>The value is silently rounded to "24.00 %" — the third decimal is discarded; `aria-invalid` is absent</t>
   </si>
   <si>
     <t>TC-SVC-BAS-008</t>
@@ -207,14 +238,19 @@
     <t>Reverting an edited field to its original value keeps Save disabled</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604 with the zero-default field APP Downloaded (service-charge-percentage-0) at 0.00 %.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads and Save is disabled |
-| 2 | Click the APP Downloaded percentage input and clear the value | Save may enable or remain disabled during the clear |
-| 3 | Type 0.00 and move focus away | Save returns to disabled - reverting to the original value must not enable Save |
-"Notes": revert-to-original probe. Revert-to-original must disable Save for numeric percentage inputs.
----</t>
+    <t>The Service Charge Basic Information page is open for office 1604 with the zero-default field APP Downloaded (service-charge-percentage-0) at 0.00 %</t>
+  </si>
+  <si>
+    <t>The tab loads and Save is disabled</t>
+  </si>
+  <si>
+    <t>2. Click the APP Downloaded percentage input and clear the value</t>
+  </si>
+  <si>
+    <t>Save may enable or remain disabled during the clear</t>
+  </si>
+  <si>
+    <t>Save returns to disabled — reverting to the original value must not enable Save</t>
   </si>
   <si>
     <t>TC-SVC-BAS-009</t>
@@ -223,15 +259,19 @@
     <t>Entering alphabetic text into a percentage field is flagged while focused</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Click the row-0 percentage field for App Quality Assurance and type abc | The letters are accepted into the field |
-| 3 | While the field is still focused, observe its invalid state | The field is flagged invalid while focused: is invalid, red border, and error icon are shown |
-| 4 | Press Tab to move focus away and observe the Save button | After focus moves away, the app may restore the stored value and clear the invalid flag; Save remains disabled throughout |
-"Notes": Negative case. Observed live: alpha input is accepted at entry, invalid while focused, and may be restored after blur; Save remains disabled.
----</t>
+    <t>2. Click the row-0 percentage field for App Quality Assurance and type abc</t>
+  </si>
+  <si>
+    <t>The letters are accepted into the field</t>
+  </si>
+  <si>
+    <t>3. While the field is still focused, observe its invalid state</t>
+  </si>
+  <si>
+    <t>The field is flagged invalid while focused: `aria-invalid="true"`, red border, and error icon are shown</t>
+  </si>
+  <si>
+    <t>After focus moves away, the app may restore the stored value and clear the invalid flag; Save remains disabled throughout</t>
   </si>
   <si>
     <t>TC-SVC-BAS-010</t>
@@ -240,15 +280,13 @@
     <t>Entering a malformed decimal value is flagged while focused</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Click the percentage input for Audio Conferencing and type 1.2.3 | The string appears verbatim in the field |
-| 3 | While the field is still focused, observe its invalid state | The string remains verbatim in the field and the field is marked invalid while focused with is invalid |
-| 4 | Press Tab to move focus away and observe the Save button | After focus leaves, the app may restore the stored value and clear the invalid marking; Save remains disabled |
-"Notes": Negative case - malformed decimal. Observed live: 1.2.3 is kept verbatim and marked invalid while focused; after blur, Save remains disabled.
----</t>
+    <t>2. Click the percentage input for Audio Conferencing and type 1.2.3</t>
+  </si>
+  <si>
+    <t>The string appears verbatim in the field</t>
+  </si>
+  <si>
+    <t>The string remains verbatim in the field and the field is marked invalid while focused with `aria-invalid="true"`</t>
   </si>
   <si>
     <t>TC-SVC-BAS-011</t>
@@ -257,15 +295,13 @@
     <t>Entering a negative number into a percentage field</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Click the percentage input for Audio Conferencing and type -5 | The value remains in the field |
-| 3 | While the field is still focused, observe its invalid state | The field is marked invalid while focused with is invalid |
-| 4 | Press Tab to move focus away and observe the Save button | After focus leaves, the app may restore the stored value and clear the invalid marking; Save remains disabled |
-"Notes": Negative case - sign constraint. Observed live: the rejection marking is reliable while focused, may clear after blur, and Save remains disabled after blur.
----</t>
+    <t>2. Click the percentage input for Audio Conferencing and type -5</t>
+  </si>
+  <si>
+    <t>The value remains in the field</t>
+  </si>
+  <si>
+    <t>The field is marked invalid while focused with `aria-invalid="true"`</t>
   </si>
   <si>
     <t>TC-SVC-BAS-012</t>
@@ -274,14 +310,16 @@
     <t>Entering a leading-zero number</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Click the percentage input for APP Downloaded and type 024 | The characters appear in the field |
-| 3 | Move focus away | The value is normalised to "24.00 %" - leading zero stripped, standard two-decimal format applied; validation error is absent |
-"Notes": Leading-zero edge case. Observed live: "024" normalises to "24.00 %" without rejection.
----</t>
+    <t>2. Click the percentage input for APP Downloaded and type 024</t>
+  </si>
+  <si>
+    <t>The characters appear in the field</t>
+  </si>
+  <si>
+    <t>3. Move focus away</t>
+  </si>
+  <si>
+    <t>The value is normalised to "24.00 %" — leading zero stripped, standard two-decimal format applied; `aria-invalid` is absent</t>
   </si>
   <si>
     <t>TC-SVC-BAS-013</t>
@@ -290,14 +328,16 @@
     <t>Entering scientific notation</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to the Basic Information tab | The tab loads |
-| 2 | Click the Audio Conferencing percentage input and type 2e1 | The characters appear |
-| 3 | Move focus away | validation error is absent - the validator accepts scientific notation as a valid numeric value; display format after normalisation is not specified |
-"Notes": Scientific notation case. Observed live: validator accepts "2e1" (validation error absent). Display format was ambiguous in the probe and is not asserted.
----</t>
+    <t>1. Navigate to the Basic Information tab</t>
+  </si>
+  <si>
+    <t>2. Click the Audio Conferencing percentage input and type 2e1</t>
+  </si>
+  <si>
+    <t>The characters appear</t>
+  </si>
+  <si>
+    <t>`aria-invalid` is absent — the validator accepts scientific notation as a valid numeric value; display format after normalisation is not specified</t>
   </si>
   <si>
     <t>TC-SVC-BAS-014</t>
@@ -306,14 +346,16 @@
     <t>Clearing a percentage field completely</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to the Basic Information tab | The tab loads |
-| 2 | Click the Audio Conferencing percentage input and select all text | All text selected |
-| 3 | Delete the selection (keyboard clear via fill) and move focus away | The application normalises the cleared field to "0.00 %" - the field does not remain empty; validation error is absent |
-"Notes": Empty value case. Keyboard-path observation: clearing via fill causes the application to restore the default "0.00 %" format. validation error absent.
----</t>
+    <t>2. Click the Audio Conferencing percentage input and select all text</t>
+  </si>
+  <si>
+    <t>All text selected</t>
+  </si>
+  <si>
+    <t>3. Delete the selection (keyboard clear via fill) and move focus away</t>
+  </si>
+  <si>
+    <t>The application normalises the cleared field to "0.00 %" — the field does not remain empty; `aria-invalid` is absent</t>
   </si>
   <si>
     <t>TC-SVC-BAS-015</t>
@@ -322,14 +364,13 @@
     <t>Entering whitespace only into a percentage field</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to the Basic Information tab | The tab loads |
-| 2 | Click the Audio Conferencing percentage input, clear it, and type spaces | Whitespace appears or is stripped |
-| 3 | Move focus away | validation error is absent - the validator does not flag whitespace-only input |
-"Notes": Whitespace-only case. Observed live: whitespace preserved in input.value; validation error absent.
----</t>
+    <t>2. Click the Audio Conferencing percentage input, clear it, and type spaces</t>
+  </si>
+  <si>
+    <t>Whitespace appears or is stripped</t>
+  </si>
+  <si>
+    <t>`aria-invalid` is absent — the validator does not flag whitespace-only input</t>
   </si>
   <si>
     <t>TC-SVC-BAS-016</t>
@@ -338,15 +379,10 @@
     <t>Pasting a very long numeric string into a percentage field</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to the Basic Information tab | The tab loads |
-| 2 | Click the APP Downloaded percentage input, clear it, and paste a 50-digit numeric string (12345678901234567890123456789012345678901234567890) | The full 50-digit string stays in the field verbatim while focused |
-| 3 | While the field is still focused, observe its invalid state | The field is marked invalid while focused with is invalid |
-| 4 | Press Tab to move focus away and observe the Save button | After focus leaves, the app may restore the stored value and clear the invalid marking; Save remains disabled |
-"Notes": Very long input case. Observed live: no truncation or scientific-notation conversion while focused; the field keeps the full string verbatim, marks it invalid while focused, and Save remains disabled after blur.
----</t>
+    <t>2. Click the APP Downloaded percentage input, clear it, and paste a 50-digit numeric string (12345678901234567890123456789012345678901234567890)</t>
+  </si>
+  <si>
+    <t>The full 50-digit string stays in the field verbatim while focused</t>
   </si>
   <si>
     <t>TC-SVC-BAS-017</t>
@@ -355,13 +391,16 @@
     <t>The percent suffix is rendered by the application, not typed by the user</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604 with inputs enabled.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to the Basic Information tab | The tab loads and inputs are enabled |
-| 2 | Read the raw input.value of service-charge-percentage-0 (APP Downloaded) without clicking it | input.value contains " %" - the application appends the percent suffix; user types the number only |
-"Notes": Format suffix observation. Observed live: input.value is "0.00 %" at rest - the percent sign is app-rendered, not user-typed.
----</t>
+    <t>The Service Charge Basic Information page is open for office 1604 with inputs enabled</t>
+  </si>
+  <si>
+    <t>The tab loads and inputs are enabled</t>
+  </si>
+  <si>
+    <t>2. Read the raw input.value of service-charge-percentage-0 (APP Downloaded) without clicking it</t>
+  </si>
+  <si>
+    <t>input.value contains " %" — the application appends the percent suffix; user types the number only</t>
   </si>
   <si>
     <t>TC-SVC-BAS-018</t>
@@ -370,14 +409,22 @@
     <t>Editing any percentage field enables the Save button</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604 and Save is disabled (no unsaved edits).
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | Save (service-charge-save) is disabled |
-| 2 | Click the percentage input for Audio Conferencing, clear it, and type 50.00 | Save transitions from disabled to enabled |
-| 3 | Reload the page without saving | Changes are discarded and Save is disabled again |
-"Notes": Save-cycle unsaved changes case. Confirms the form enters a unsaved changes immediately on any edit.
----</t>
+    <t>The Service Charge Basic Information page is open for office 1604 and Save is disabled (no unsaved edits)</t>
+  </si>
+  <si>
+    <t>Save (`service-charge-save`) is disabled</t>
+  </si>
+  <si>
+    <t>2. Click the percentage input for Audio Conferencing, clear it, and type 50.00</t>
+  </si>
+  <si>
+    <t>Save transitions from disabled to enabled</t>
+  </si>
+  <si>
+    <t>3. Reload the page without saving</t>
+  </si>
+  <si>
+    <t>Changes are discarded and Save is disabled again</t>
   </si>
   <si>
     <t>TC-SVC-BAS-019</t>
@@ -386,14 +433,22 @@
     <t>Reverting an edited percentage field to its original value disables Save</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604 and Save is disabled.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | Save is disabled |
-| 2 | Click the Audio Conferencing percentage input, clear it, and type 50.00 | Save becomes enabled |
-| 3 | Clear the field again and type 24.00 (the original value) and move focus away | Save returns to disabled - reverting to the original value must not leave the form dirty |
-"Notes": revert-to-original-disables-Save. The original value must be known (from inventory or a prior read); 24.00 is the documented default for row 8.
----</t>
+    <t>The Service Charge Basic Information page is open for office 1604 and Save is disabled</t>
+  </si>
+  <si>
+    <t>Save is disabled</t>
+  </si>
+  <si>
+    <t>2. Click the Audio Conferencing percentage input, clear it, and type 50.00</t>
+  </si>
+  <si>
+    <t>Save becomes enabled</t>
+  </si>
+  <si>
+    <t>3. Clear the field again and type 24.00 (the original value) and move focus away</t>
+  </si>
+  <si>
+    <t>Save returns to disabled — reverting to the original value must not leave the form dirty</t>
   </si>
   <si>
     <t>TC-SVC-BAS-020</t>
@@ -402,16 +457,25 @@
     <t>Saving an edited percentage field persists the new value after reload</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604 and the Audio Conferencing field shows 24.00 %.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads with Audio Conferencing showing 24.00 % |
-| 2 | Click the percentage input for Audio Conferencing, clear it, and type 30.00 | The field shows 30.00 and Save enables |
-| 3 | Click Save | Save completes; no error dialog |
-| 4 | Reload the page and re-open the Basic Information tab | Audio Conferencing shows 30.00 % |
-| 5 | Click the field, clear it, type 24.00, and click Save | The field is restored to 24.00 % and Save completes |
-"Notes": Save-cycle new-fill case with Tier 1 baseline restore. Step 5 restores the shared environment to the documented default so subsequent test runs start from the same baseline.
----</t>
+    <t>The Service Charge Basic Information page is open for office 1604 and the Audio Conferencing field shows 24.00 %</t>
+  </si>
+  <si>
+    <t>The tab loads with Audio Conferencing showing `24.00 %`</t>
+  </si>
+  <si>
+    <t>The field shows `30.00` and Save enables</t>
+  </si>
+  <si>
+    <t>Save completes; no error dialog</t>
+  </si>
+  <si>
+    <t>Audio Conferencing shows `30.00 %`</t>
+  </si>
+  <si>
+    <t>5. Click the field, clear it, type 24.00, and click Save</t>
+  </si>
+  <si>
+    <t>The field is restored to `24.00 %` and Save completes</t>
   </si>
   <si>
     <t>TC-SVC-BAS-021</t>
@@ -420,17 +484,34 @@
     <t>Overwriting an edited value before saving persists the second value</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604 and Audio Conferencing shows 24.00 %.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Click the Audio Conferencing percentage input and type 30.00 | Save enables |
-| 3 | Without saving, clear the field again and type 40.00 | The field shows 40.00; Save remains enabled |
-| 4 | Click Save | Save completes |
-| 5 | Reload the page | Audio Conferencing shows 40.00 % - only the final pre-save value was persisted |
-| 6 | Restore: click the field, clear it, type 24.00, and click Save | The field is restored to 24.00 % |
-"Notes": Edit-overwrite save-cycle case. Confirms that intermediate values are not persisted.
----</t>
+    <t>The Service Charge Basic Information page is open for office 1604 and Audio Conferencing shows 24.00 %</t>
+  </si>
+  <si>
+    <t>2. Click the Audio Conferencing percentage input and type 30.00</t>
+  </si>
+  <si>
+    <t>Save enables</t>
+  </si>
+  <si>
+    <t>3. Without saving, clear the field again and type 40.00</t>
+  </si>
+  <si>
+    <t>The field shows `40.00`; Save remains enabled</t>
+  </si>
+  <si>
+    <t>4. Click Save</t>
+  </si>
+  <si>
+    <t>Save completes</t>
+  </si>
+  <si>
+    <t>5. Reload the page</t>
+  </si>
+  <si>
+    <t>Audio Conferencing shows `40.00 %` — only the final pre-save value was persisted</t>
+  </si>
+  <si>
+    <t>6. Restore: click the field, clear it, type 24.00, and click Save</t>
   </si>
   <si>
     <t>TC-SVC-BAS-022</t>
@@ -439,15 +520,22 @@
     <t>Navigating away from the page with unsaved edits triggers a confirmation prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Edit any percentage field so that Save enables | Save is enabled (form is dirty) |
-| 3 | Press the browser Back button | The browser's native leave-page dialog appears (type: beforeunload). Browser-back triggers the browser's native dialog; in-app tab navigation shows the application's "Unsaved changes" modal (Stay / Discard). Both behaviours were confirmed on the live site. |
-| 4 | Dismiss the dialog (stay on page) | Navigation is cancelled; the page remains open with the edit still present. Reload or discard the edit to restore clean state. |
-"Notes": Browser-back fires the browser's native beforeunload dialog. In-app tab navigation (e.g. clicking the History tab) shows the application's own "Unsaved changes" modal instead - that path is covered by TC-SVC-HIS-014.
----</t>
+    <t>2. Edit any percentage field so that Save enables</t>
+  </si>
+  <si>
+    <t>Save is enabled (form is dirty)</t>
+  </si>
+  <si>
+    <t>3. Press the browser Back button</t>
+  </si>
+  <si>
+    <t>The browser's native leave-page dialog appears (type: `beforeunload`). Browser-back triggers the browser's native dialog; in-app tab navigation shows the application's "Unsaved changes" modal (Stay / Discard). Both behaviours were confirmed on the live site.</t>
+  </si>
+  <si>
+    <t>4. Dismiss the dialog (stay on page)</t>
+  </si>
+  <si>
+    <t>Navigation is cancelled; the page remains open with the edit still present. Reload or discard the edit to restore clean state.</t>
   </si>
   <si>
     <t>TC-SVC-BAS-023</t>
@@ -456,17 +544,25 @@
     <t>Saving edits to multiple percentage fields in a single Save action</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Edit the Audio Conferencing field to 30.00 | Save enables |
-| 3 | Edit the Equipment Rental field (service-charge-percentage-23) to 25.00 | Save remains enabled |
-| 4 | Click Save | Save completes without error |
-| 5 | Reload the page and re-open the Basic Information tab | Both Audio Conferencing reads 30.00 % and Equipment Rental reads 25.00 % |
-| 6 | Restore: return both fields to their original values (24.00 % each) and click Save | Both fields are restored |
-"Notes": Bulk save-cycle case. Confirms there is no partial-save behaviour when multiple fields are edited simultaneously.
----</t>
+    <t>2. Edit the Audio Conferencing field to 30.00</t>
+  </si>
+  <si>
+    <t>3. Edit the Equipment Rental field (service-charge-percentage-23) to 25.00</t>
+  </si>
+  <si>
+    <t>Save remains enabled</t>
+  </si>
+  <si>
+    <t>5. Reload the page and re-open the Basic Information tab</t>
+  </si>
+  <si>
+    <t>Both Audio Conferencing reads `30.00 %` and Equipment Rental reads `25.00 %`</t>
+  </si>
+  <si>
+    <t>6. Restore: return both fields to their original values (24.00 % each) and click Save</t>
+  </si>
+  <si>
+    <t>Both fields are restored</t>
   </si>
   <si>
     <t>TC-SVC-BAS-024</t>
@@ -475,14 +571,16 @@
     <t>Service Type column renders correct labels</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Read the Service Type label for row 8 | The label reads "Audio Conferencing" - matches the inventory-catalogued name for that index |
-| 3 | Read the Service Type label for row 0 | The label reads "APP Downloaded" |
-"Notes": Render-state assertion for the read-only label column. Verifies the label column is populated with the correct service type names and is not truncated or empty.
----</t>
+    <t>2. Read the Service Type label for row 8</t>
+  </si>
+  <si>
+    <t>The label reads "Audio Conferencing" — matches the inventory-catalogued name for that index</t>
+  </si>
+  <si>
+    <t>3. Read the Service Type label for row 0</t>
+  </si>
+  <si>
+    <t>The label reads "APP Downloaded"</t>
   </si>
   <si>
     <t>TC-SVC-BAS-025</t>
@@ -491,14 +589,16 @@
     <t>Clicking a Service Type label cell does not open any editor or dialog</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Click the Service Type label cell for Audio Conferencing | No editor opens, no dialog appears, and Save remains disabled |
-| 3 | Click the Service Type label cell for APP Downloaded | Same result - the cell is static and non-interactive |
-"Notes": Affordance check. Inventory records affordance: none for the Service Type column; this case confirms the classification is correct. Save must remain disabled because no data was changed.
----</t>
+    <t>2. Click the Service Type label cell for Audio Conferencing</t>
+  </si>
+  <si>
+    <t>No editor opens, no dialog appears, and Save remains disabled</t>
+  </si>
+  <si>
+    <t>3. Click the Service Type label cell for APP Downloaded</t>
+  </si>
+  <si>
+    <t>Same result — the cell is static and non-interactive</t>
   </si>
   <si>
     <t>TC-SVC-BAS-026</t>
@@ -507,13 +607,16 @@
     <t>Save button is disabled on page load with no edits</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page for office 1604 has just been loaded with no prior unsaved changes.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The page loads |
-| 2 | Without making any edit, read the disabled state of the Save button (service-charge-save) | The Save button has the is disabled - it is not clickable |
-"Notes": Save-state at rest. Confirms the default clean state.
----</t>
+    <t>The Service Charge Basic Information page for office 1604 has just been loaded with no prior unsaved changes</t>
+  </si>
+  <si>
+    <t>The page loads</t>
+  </si>
+  <si>
+    <t>2. Without making any edit, read the disabled state of the Save button (service-charge-save)</t>
+  </si>
+  <si>
+    <t>The Save button has the `disabled` attribute — it is not clickable</t>
   </si>
   <si>
     <t>TC-SVC-BAS-027</t>
@@ -522,14 +625,7 @@
     <t>Save button enables after any percentage edit</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604 and Save is disabled.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | Save is disabled |
-| 2 | Click the Audio Conferencing percentage input, clear it, and type 50.00 | Save loses its is disabled and becomes clickable |
-| 3 | Reload the page without saving | Changes are discarded and Save is disabled again |
-"Notes": Save enablement after a single edit. Confirms the unsaved changes detection fires on any field change.
----</t>
+    <t>Save loses its `disabled` attribute and becomes clickable</t>
   </si>
   <si>
     <t>TC-SVC-BAS-028</t>
@@ -538,13 +634,10 @@
     <t>Column headers render with correct labels</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Read the text of the two column headers | The headers read exactly Service Type and Service Charge Percentage (two columns, no extra columns, no truncation) |
-"Notes": QUICK must-assert for the render-state. Verbatim column header check. Values sourced from the field inventory walk.
----</t>
+    <t>2. Read the text of the two column headers</t>
+  </si>
+  <si>
+    <t>The headers read exactly `Service Type` and `Service Charge Percentage` (two columns, no extra columns, no truncation)</t>
   </si>
   <si>
     <t>TC-SVC-BAS-029</t>
@@ -553,15 +646,29 @@
     <t>All 79 rows render and a named row is readable without scrolling</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Count the total number of data rows in the table | 79 rows are present |
-| 3 | Locate the row with Service Type "Audio Conferencing" using a content | The row is readable and its percentage input (service-charge-percentage-8) is accessible |
-| 4 | NEEDS-LIVE-CONFIRM: verify that no pagination control or "load more" button is present | No pagination control exists - all 79 rows are displayed at once |
-"Notes": QUICK must-assert for the empty-vol. Confirms the table is fully populated and no row is hidden behind pagination or virtualization. content-based row read (not position).
----</t>
+    <t xml:space="preserve">User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Audio Conferencing"
+Sample input 2: "load more"</t>
+  </si>
+  <si>
+    <t>2. Count the total number of data rows in the table</t>
+  </si>
+  <si>
+    <t>79 rows are present</t>
+  </si>
+  <si>
+    <t>3. Locate the row with Service Type "Audio Conferencing" using a content</t>
+  </si>
+  <si>
+    <t>The row is readable and its percentage input (`service-charge-percentage-8`) is accessible</t>
+  </si>
+  <si>
+    <t>4. NEEDS-LIVE-CONFIRM: verify that no pagination control or "load more" button is present</t>
+  </si>
+  <si>
+    <t>No pagination control exists — all 79 rows are displayed at once</t>
   </si>
   <si>
     <t>TC-SVC-BAS-030</t>
@@ -570,15 +677,22 @@
     <t>A saved value persists after page reload (surface persistence)</t>
   </si>
   <si>
-    <t xml:space="preserve">The Service Charge Basic Information page is open for office 1604.
-| # | Step | Expected Result |
-|---|------|-----------------|
-| 1 | Navigate to Location Settings for office 1604 and open the Basic Information tab | The tab loads |
-| 2 | Edit the Audio Conferencing percentage to a new value and click Save | Save completes |
-| 3 | Reload the page and re-open the Basic Information tab | The edited value is still shown - the change survived a full page reload |
-| 4 | NEEDS-LIVE-CONFIRM: verify that no column sort affordance (sortable column header) is present | No sort control is present - row order is application-defined and fixed |
-| 5 | Restore: return the field to its original value and save | The field is restored |
-"Notes": QUICK must-assert for the persistence. Confirms saved data survives a reload. Also carries the sorting-absence verification from the catalog's out-of-scope note (NEEDS-LIVE-CONFIRM pending a live enabled walk)</t>
+    <t>2. Edit the Audio Conferencing percentage to a new value and click Save</t>
+  </si>
+  <si>
+    <t>3. Reload the page and re-open the Basic Information tab</t>
+  </si>
+  <si>
+    <t>The edited value is still shown — the change survived a full page reload</t>
+  </si>
+  <si>
+    <t>4. NEEDS-LIVE-CONFIRM: verify that no column sort affordance (sortable column header) is present</t>
+  </si>
+  <si>
+    <t>No sort control is present — row order is application-defined and fixed</t>
+  </si>
+  <si>
+    <t>5. Restore: return the field to its original value and save</t>
   </si>
   <si>
     <t>SUMMARY</t>
@@ -593,10 +707,10 @@
     <t>Pass:30 Fail:0 Skipped:0 Blocked:0</t>
   </si>
   <si>
-    <t>Last Updated: 2026-08-15</t>
-  </si>
-  <si>
-    <t>6729770ff2e77acf7dfad5e1019f025e9612e9fa3d5a8ea5b9a5f4adb8ffb470</t>
+    <t>Last Updated: 2026-08-18</t>
+  </si>
+  <si>
+    <t>216e3ef472e1d1a5fd8bdc823b2299e2983f8e64bb024549c10be824c756f7bc</t>
   </si>
 </sst>
 </file>
@@ -985,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M113"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -996,9 +1110,7 @@
     <col min="6" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
     <col min="9" max="9" width="36" customWidth="1"/>
-    <col min="10" max="10" width="80" customWidth="1"/>
-    <col min="11" max="11" width="23" customWidth="1"/>
-    <col min="12" max="12" width="25" customWidth="1"/>
+    <col min="10" max="12" width="80" customWidth="1"/>
     <col min="13" max="13" width="26" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1081,7 +1193,7 @@
         <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -1089,130 +1201,130 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>27</v>
       </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
       <c r="M3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" t="s">
+      <c r="L4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
       <c r="M4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" t="s">
-        <v>24</v>
-      </c>
       <c r="M5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -1236,7 +1348,7 @@
         <v>21</v>
       </c>
       <c r="J6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
         <v>23</v>
@@ -1245,138 +1357,138 @@
         <v>24</v>
       </c>
       <c r="M6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L7" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="K8" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="L8" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="M8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J9" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="L9" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="M9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
@@ -1400,147 +1512,147 @@
         <v>21</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K10" t="s">
         <v>23</v>
       </c>
       <c r="L10" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="M10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J11" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L11" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="M11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="L12" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="M12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J13" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="K13" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="L13" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="M13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -1564,188 +1676,188 @@
         <v>21</v>
       </c>
       <c r="J14" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K14" t="s">
         <v>23</v>
       </c>
       <c r="L14" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="M14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J15" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="K15" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="L15" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="M15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J16" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="K16" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="L16" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="M16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J17" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="K17" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="L17" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="M17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G18" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J18" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="K18" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="L18" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="M18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
         <v>15</v>
@@ -1769,147 +1881,147 @@
         <v>21</v>
       </c>
       <c r="J19" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="K19" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="L19" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="M19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G20" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J20" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="K20" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L20" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="M20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G21" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H21" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J21" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="K21" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="L21" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="M21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G22" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J22" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="K22" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="L22" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="M22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
         <v>15</v>
@@ -1933,147 +2045,147 @@
         <v>21</v>
       </c>
       <c r="J23" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="K23" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="L23" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="M23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G24" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H24" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J24" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="K24" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L24" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="M24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H25" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J25" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K25" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="L25" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="M25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F26" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G26" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J26" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="L26" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="M26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
         <v>15</v>
@@ -2097,106 +2209,106 @@
         <v>21</v>
       </c>
       <c r="J27" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="K27" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="L27" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="M27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G28" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H28" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J28" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="K28" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L28" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="M28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G29" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H29" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J29" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="K29" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="L29" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="M29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
         <v>15</v>
@@ -2220,98 +2332,3378 @@
         <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="K30" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="L30" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="M30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" t="s">
+        <v>25</v>
+      </c>
+      <c r="I31" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" t="s">
+        <v>76</v>
+      </c>
+      <c r="L31" t="s">
+        <v>77</v>
+      </c>
+      <c r="M31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" t="s">
+        <v>25</v>
+      </c>
+      <c r="I32" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" t="s">
+        <v>37</v>
+      </c>
+      <c r="L32" t="s">
+        <v>78</v>
+      </c>
+      <c r="M32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>42</v>
+      </c>
+      <c r="K33" t="s">
+        <v>60</v>
+      </c>
+      <c r="L33" t="s">
+        <v>43</v>
+      </c>
+      <c r="M33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" t="s">
+        <v>25</v>
+      </c>
+      <c r="I34" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" t="s">
+        <v>25</v>
+      </c>
+      <c r="K34" t="s">
+        <v>81</v>
+      </c>
+      <c r="L34" t="s">
+        <v>82</v>
+      </c>
+      <c r="M34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" t="s">
+        <v>25</v>
+      </c>
+      <c r="I35" t="s">
+        <v>25</v>
+      </c>
+      <c r="J35" t="s">
+        <v>25</v>
+      </c>
+      <c r="K35" t="s">
+        <v>83</v>
+      </c>
+      <c r="L35" t="s">
+        <v>84</v>
+      </c>
+      <c r="M35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36" t="s">
+        <v>25</v>
+      </c>
+      <c r="H36" t="s">
+        <v>25</v>
+      </c>
+      <c r="I36" t="s">
+        <v>25</v>
+      </c>
+      <c r="J36" t="s">
+        <v>25</v>
+      </c>
+      <c r="K36" t="s">
+        <v>63</v>
+      </c>
+      <c r="L36" t="s">
+        <v>85</v>
+      </c>
+      <c r="M36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>42</v>
+      </c>
+      <c r="K37" t="s">
+        <v>60</v>
+      </c>
+      <c r="L37" t="s">
+        <v>43</v>
+      </c>
+      <c r="M37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" t="s">
+        <v>25</v>
+      </c>
+      <c r="I38" t="s">
+        <v>25</v>
+      </c>
+      <c r="J38" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" t="s">
+        <v>88</v>
+      </c>
+      <c r="L38" t="s">
+        <v>89</v>
+      </c>
+      <c r="M38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" t="s">
+        <v>25</v>
+      </c>
+      <c r="H39" t="s">
+        <v>25</v>
+      </c>
+      <c r="I39" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" t="s">
+        <v>25</v>
+      </c>
+      <c r="K39" t="s">
+        <v>83</v>
+      </c>
+      <c r="L39" t="s">
+        <v>90</v>
+      </c>
+      <c r="M39" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" t="s">
+        <v>25</v>
+      </c>
+      <c r="H40" t="s">
+        <v>25</v>
+      </c>
+      <c r="I40" t="s">
+        <v>25</v>
+      </c>
+      <c r="J40" t="s">
+        <v>25</v>
+      </c>
+      <c r="K40" t="s">
+        <v>63</v>
+      </c>
+      <c r="L40" t="s">
+        <v>64</v>
+      </c>
+      <c r="M40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K41" t="s">
+        <v>60</v>
+      </c>
+      <c r="L41" t="s">
+        <v>43</v>
+      </c>
+      <c r="M41" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" t="s">
+        <v>25</v>
+      </c>
+      <c r="H42" t="s">
+        <v>25</v>
+      </c>
+      <c r="I42" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K42" t="s">
+        <v>93</v>
+      </c>
+      <c r="L42" t="s">
+        <v>94</v>
+      </c>
+      <c r="M42" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" t="s">
+        <v>25</v>
+      </c>
+      <c r="H43" t="s">
+        <v>25</v>
+      </c>
+      <c r="I43" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K43" t="s">
+        <v>83</v>
+      </c>
+      <c r="L43" t="s">
+        <v>95</v>
+      </c>
+      <c r="M43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44" t="s">
+        <v>25</v>
+      </c>
+      <c r="H44" t="s">
+        <v>25</v>
+      </c>
+      <c r="I44" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" t="s">
+        <v>25</v>
+      </c>
+      <c r="K44" t="s">
+        <v>63</v>
+      </c>
+      <c r="L44" t="s">
+        <v>64</v>
+      </c>
+      <c r="M44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s">
+        <v>42</v>
+      </c>
+      <c r="K45" t="s">
+        <v>60</v>
+      </c>
+      <c r="L45" t="s">
+        <v>43</v>
+      </c>
+      <c r="M45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" t="s">
+        <v>25</v>
+      </c>
+      <c r="H46" t="s">
+        <v>25</v>
+      </c>
+      <c r="I46" t="s">
+        <v>25</v>
+      </c>
+      <c r="J46" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" t="s">
+        <v>98</v>
+      </c>
+      <c r="L46" t="s">
+        <v>99</v>
+      </c>
+      <c r="M46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" t="s">
+        <v>25</v>
+      </c>
+      <c r="H47" t="s">
+        <v>25</v>
+      </c>
+      <c r="I47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K47" t="s">
+        <v>100</v>
+      </c>
+      <c r="L47" t="s">
+        <v>101</v>
+      </c>
+      <c r="M47" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" t="s">
+        <v>103</v>
+      </c>
+      <c r="C48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s">
+        <v>42</v>
+      </c>
+      <c r="K48" t="s">
+        <v>104</v>
+      </c>
+      <c r="L48" t="s">
+        <v>43</v>
+      </c>
+      <c r="M48" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" t="s">
+        <v>25</v>
+      </c>
+      <c r="H49" t="s">
+        <v>25</v>
+      </c>
+      <c r="I49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J49" t="s">
+        <v>25</v>
+      </c>
+      <c r="K49" t="s">
+        <v>105</v>
+      </c>
+      <c r="L49" t="s">
+        <v>106</v>
+      </c>
+      <c r="M49" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50" t="s">
+        <v>25</v>
+      </c>
+      <c r="H50" t="s">
+        <v>25</v>
+      </c>
+      <c r="I50" t="s">
+        <v>25</v>
+      </c>
+      <c r="J50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K50" t="s">
+        <v>100</v>
+      </c>
+      <c r="L50" t="s">
+        <v>107</v>
+      </c>
+      <c r="M50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" t="s">
         <v>109</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>42</v>
+      </c>
+      <c r="K51" t="s">
+        <v>104</v>
+      </c>
+      <c r="L51" t="s">
+        <v>43</v>
+      </c>
+      <c r="M51" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" t="s">
+        <v>25</v>
+      </c>
+      <c r="G52" t="s">
+        <v>25</v>
+      </c>
+      <c r="H52" t="s">
+        <v>25</v>
+      </c>
+      <c r="I52" t="s">
+        <v>25</v>
+      </c>
+      <c r="J52" t="s">
+        <v>25</v>
+      </c>
+      <c r="K52" t="s">
         <v>110</v>
       </c>
-      <c r="C31" t="s">
+      <c r="L52" t="s">
+        <v>111</v>
+      </c>
+      <c r="M52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" t="s">
+        <v>25</v>
+      </c>
+      <c r="H53" t="s">
+        <v>25</v>
+      </c>
+      <c r="I53" t="s">
+        <v>25</v>
+      </c>
+      <c r="J53" t="s">
+        <v>25</v>
+      </c>
+      <c r="K53" t="s">
+        <v>112</v>
+      </c>
+      <c r="L53" t="s">
+        <v>113</v>
+      </c>
+      <c r="M53" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54" t="s">
         <v>15</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D54" t="s">
         <v>16</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E54" t="s">
         <v>17</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F54" t="s">
         <v>18</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G54" t="s">
         <v>19</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H54" t="s">
         <v>20</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I54" t="s">
         <v>21</v>
       </c>
-      <c r="J31" t="s">
-        <v>111</v>
-      </c>
-      <c r="K31" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" t="s">
-        <v>24</v>
-      </c>
-      <c r="M31" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M33" s="2" t="s">
+      <c r="J54" t="s">
+        <v>42</v>
+      </c>
+      <c r="K54" t="s">
+        <v>104</v>
+      </c>
+      <c r="L54" t="s">
+        <v>43</v>
+      </c>
+      <c r="M54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" t="s">
+        <v>25</v>
+      </c>
+      <c r="G55" t="s">
+        <v>25</v>
+      </c>
+      <c r="H55" t="s">
+        <v>25</v>
+      </c>
+      <c r="I55" t="s">
+        <v>25</v>
+      </c>
+      <c r="J55" t="s">
+        <v>25</v>
+      </c>
+      <c r="K55" t="s">
         <v>116</v>
+      </c>
+      <c r="L55" t="s">
+        <v>117</v>
+      </c>
+      <c r="M55" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" t="s">
+        <v>25</v>
+      </c>
+      <c r="G56" t="s">
+        <v>25</v>
+      </c>
+      <c r="H56" t="s">
+        <v>25</v>
+      </c>
+      <c r="I56" t="s">
+        <v>25</v>
+      </c>
+      <c r="J56" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" t="s">
+        <v>100</v>
+      </c>
+      <c r="L56" t="s">
+        <v>118</v>
+      </c>
+      <c r="M56" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>119</v>
+      </c>
+      <c r="B57" t="s">
+        <v>120</v>
+      </c>
+      <c r="C57" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s">
+        <v>42</v>
+      </c>
+      <c r="K57" t="s">
+        <v>104</v>
+      </c>
+      <c r="L57" t="s">
+        <v>43</v>
+      </c>
+      <c r="M57" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" t="s">
+        <v>25</v>
+      </c>
+      <c r="G58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H58" t="s">
+        <v>25</v>
+      </c>
+      <c r="I58" t="s">
+        <v>25</v>
+      </c>
+      <c r="J58" t="s">
+        <v>25</v>
+      </c>
+      <c r="K58" t="s">
+        <v>121</v>
+      </c>
+      <c r="L58" t="s">
+        <v>122</v>
+      </c>
+      <c r="M58" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" t="s">
+        <v>25</v>
+      </c>
+      <c r="D59" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" t="s">
+        <v>25</v>
+      </c>
+      <c r="G59" t="s">
+        <v>25</v>
+      </c>
+      <c r="H59" t="s">
+        <v>25</v>
+      </c>
+      <c r="I59" t="s">
+        <v>25</v>
+      </c>
+      <c r="J59" t="s">
+        <v>25</v>
+      </c>
+      <c r="K59" t="s">
+        <v>83</v>
+      </c>
+      <c r="L59" t="s">
+        <v>95</v>
+      </c>
+      <c r="M59" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" t="s">
+        <v>25</v>
+      </c>
+      <c r="G60" t="s">
+        <v>25</v>
+      </c>
+      <c r="H60" t="s">
+        <v>25</v>
+      </c>
+      <c r="I60" t="s">
+        <v>25</v>
+      </c>
+      <c r="J60" t="s">
+        <v>25</v>
+      </c>
+      <c r="K60" t="s">
+        <v>63</v>
+      </c>
+      <c r="L60" t="s">
+        <v>64</v>
+      </c>
+      <c r="M60" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61" t="s">
+        <v>124</v>
+      </c>
+      <c r="C61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>125</v>
+      </c>
+      <c r="K61" t="s">
+        <v>104</v>
+      </c>
+      <c r="L61" t="s">
+        <v>126</v>
+      </c>
+      <c r="M61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" t="s">
+        <v>25</v>
+      </c>
+      <c r="D62" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" t="s">
+        <v>25</v>
+      </c>
+      <c r="G62" t="s">
+        <v>25</v>
+      </c>
+      <c r="H62" t="s">
+        <v>25</v>
+      </c>
+      <c r="I62" t="s">
+        <v>25</v>
+      </c>
+      <c r="J62" t="s">
+        <v>25</v>
+      </c>
+      <c r="K62" t="s">
+        <v>127</v>
+      </c>
+      <c r="L62" t="s">
+        <v>128</v>
+      </c>
+      <c r="M62" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>129</v>
+      </c>
+      <c r="B63" t="s">
+        <v>130</v>
+      </c>
+      <c r="C63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s">
+        <v>131</v>
+      </c>
+      <c r="K63" t="s">
+        <v>60</v>
+      </c>
+      <c r="L63" t="s">
+        <v>132</v>
+      </c>
+      <c r="M63" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" t="s">
+        <v>25</v>
+      </c>
+      <c r="D64" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" t="s">
+        <v>25</v>
+      </c>
+      <c r="H64" t="s">
+        <v>25</v>
+      </c>
+      <c r="I64" t="s">
+        <v>25</v>
+      </c>
+      <c r="J64" t="s">
+        <v>25</v>
+      </c>
+      <c r="K64" t="s">
+        <v>133</v>
+      </c>
+      <c r="L64" t="s">
+        <v>134</v>
+      </c>
+      <c r="M64" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65" t="s">
+        <v>25</v>
+      </c>
+      <c r="D65" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" t="s">
+        <v>25</v>
+      </c>
+      <c r="G65" t="s">
+        <v>25</v>
+      </c>
+      <c r="H65" t="s">
+        <v>25</v>
+      </c>
+      <c r="I65" t="s">
+        <v>25</v>
+      </c>
+      <c r="J65" t="s">
+        <v>25</v>
+      </c>
+      <c r="K65" t="s">
+        <v>135</v>
+      </c>
+      <c r="L65" t="s">
+        <v>136</v>
+      </c>
+      <c r="M65" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>137</v>
+      </c>
+      <c r="B66" t="s">
+        <v>138</v>
+      </c>
+      <c r="C66" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>139</v>
+      </c>
+      <c r="K66" t="s">
+        <v>60</v>
+      </c>
+      <c r="L66" t="s">
+        <v>140</v>
+      </c>
+      <c r="M66" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" t="s">
+        <v>25</v>
+      </c>
+      <c r="D67" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" t="s">
+        <v>25</v>
+      </c>
+      <c r="G67" t="s">
+        <v>25</v>
+      </c>
+      <c r="H67" t="s">
+        <v>25</v>
+      </c>
+      <c r="I67" t="s">
+        <v>25</v>
+      </c>
+      <c r="J67" t="s">
+        <v>25</v>
+      </c>
+      <c r="K67" t="s">
+        <v>141</v>
+      </c>
+      <c r="L67" t="s">
+        <v>142</v>
+      </c>
+      <c r="M67" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" t="s">
+        <v>25</v>
+      </c>
+      <c r="D68" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" t="s">
+        <v>25</v>
+      </c>
+      <c r="G68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H68" t="s">
+        <v>25</v>
+      </c>
+      <c r="I68" t="s">
+        <v>25</v>
+      </c>
+      <c r="J68" t="s">
+        <v>25</v>
+      </c>
+      <c r="K68" t="s">
+        <v>143</v>
+      </c>
+      <c r="L68" t="s">
+        <v>144</v>
+      </c>
+      <c r="M68" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" t="s">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s">
+        <v>147</v>
+      </c>
+      <c r="K69" t="s">
+        <v>60</v>
+      </c>
+      <c r="L69" t="s">
+        <v>148</v>
+      </c>
+      <c r="M69" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70" t="s">
+        <v>25</v>
+      </c>
+      <c r="D70" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" t="s">
+        <v>25</v>
+      </c>
+      <c r="F70" t="s">
+        <v>25</v>
+      </c>
+      <c r="G70" t="s">
+        <v>25</v>
+      </c>
+      <c r="H70" t="s">
+        <v>25</v>
+      </c>
+      <c r="I70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J70" t="s">
+        <v>25</v>
+      </c>
+      <c r="K70" t="s">
+        <v>51</v>
+      </c>
+      <c r="L70" t="s">
+        <v>149</v>
+      </c>
+      <c r="M70" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71" t="s">
+        <v>25</v>
+      </c>
+      <c r="D71" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" t="s">
+        <v>25</v>
+      </c>
+      <c r="F71" t="s">
+        <v>25</v>
+      </c>
+      <c r="G71" t="s">
+        <v>25</v>
+      </c>
+      <c r="H71" t="s">
+        <v>25</v>
+      </c>
+      <c r="I71" t="s">
+        <v>25</v>
+      </c>
+      <c r="J71" t="s">
+        <v>25</v>
+      </c>
+      <c r="K71" t="s">
+        <v>53</v>
+      </c>
+      <c r="L71" t="s">
+        <v>150</v>
+      </c>
+      <c r="M71" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C72" t="s">
+        <v>25</v>
+      </c>
+      <c r="D72" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72" t="s">
+        <v>25</v>
+      </c>
+      <c r="G72" t="s">
+        <v>25</v>
+      </c>
+      <c r="H72" t="s">
+        <v>25</v>
+      </c>
+      <c r="I72" t="s">
+        <v>25</v>
+      </c>
+      <c r="J72" t="s">
+        <v>25</v>
+      </c>
+      <c r="K72" t="s">
+        <v>55</v>
+      </c>
+      <c r="L72" t="s">
+        <v>151</v>
+      </c>
+      <c r="M72" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>25</v>
+      </c>
+      <c r="C73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" t="s">
+        <v>25</v>
+      </c>
+      <c r="G73" t="s">
+        <v>25</v>
+      </c>
+      <c r="H73" t="s">
+        <v>25</v>
+      </c>
+      <c r="I73" t="s">
+        <v>25</v>
+      </c>
+      <c r="J73" t="s">
+        <v>25</v>
+      </c>
+      <c r="K73" t="s">
+        <v>152</v>
+      </c>
+      <c r="L73" t="s">
+        <v>153</v>
+      </c>
+      <c r="M73" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>154</v>
+      </c>
+      <c r="B74" t="s">
+        <v>155</v>
+      </c>
+      <c r="C74" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>156</v>
+      </c>
+      <c r="K74" t="s">
+        <v>60</v>
+      </c>
+      <c r="L74" t="s">
+        <v>43</v>
+      </c>
+      <c r="M74" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" t="s">
+        <v>25</v>
+      </c>
+      <c r="D75" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75" t="s">
+        <v>25</v>
+      </c>
+      <c r="G75" t="s">
+        <v>25</v>
+      </c>
+      <c r="H75" t="s">
+        <v>25</v>
+      </c>
+      <c r="I75" t="s">
+        <v>25</v>
+      </c>
+      <c r="J75" t="s">
+        <v>25</v>
+      </c>
+      <c r="K75" t="s">
+        <v>157</v>
+      </c>
+      <c r="L75" t="s">
+        <v>158</v>
+      </c>
+      <c r="M75" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" t="s">
+        <v>25</v>
+      </c>
+      <c r="C76" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" t="s">
+        <v>25</v>
+      </c>
+      <c r="F76" t="s">
+        <v>25</v>
+      </c>
+      <c r="G76" t="s">
+        <v>25</v>
+      </c>
+      <c r="H76" t="s">
+        <v>25</v>
+      </c>
+      <c r="I76" t="s">
+        <v>25</v>
+      </c>
+      <c r="J76" t="s">
+        <v>25</v>
+      </c>
+      <c r="K76" t="s">
+        <v>159</v>
+      </c>
+      <c r="L76" t="s">
+        <v>160</v>
+      </c>
+      <c r="M76" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77" t="s">
+        <v>25</v>
+      </c>
+      <c r="C77" t="s">
+        <v>25</v>
+      </c>
+      <c r="D77" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" t="s">
+        <v>25</v>
+      </c>
+      <c r="F77" t="s">
+        <v>25</v>
+      </c>
+      <c r="G77" t="s">
+        <v>25</v>
+      </c>
+      <c r="H77" t="s">
+        <v>25</v>
+      </c>
+      <c r="I77" t="s">
+        <v>25</v>
+      </c>
+      <c r="J77" t="s">
+        <v>25</v>
+      </c>
+      <c r="K77" t="s">
+        <v>161</v>
+      </c>
+      <c r="L77" t="s">
+        <v>162</v>
+      </c>
+      <c r="M77" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>25</v>
+      </c>
+      <c r="C78" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" t="s">
+        <v>25</v>
+      </c>
+      <c r="F78" t="s">
+        <v>25</v>
+      </c>
+      <c r="G78" t="s">
+        <v>25</v>
+      </c>
+      <c r="H78" t="s">
+        <v>25</v>
+      </c>
+      <c r="I78" t="s">
+        <v>25</v>
+      </c>
+      <c r="J78" t="s">
+        <v>25</v>
+      </c>
+      <c r="K78" t="s">
+        <v>163</v>
+      </c>
+      <c r="L78" t="s">
+        <v>164</v>
+      </c>
+      <c r="M78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" t="s">
+        <v>25</v>
+      </c>
+      <c r="D79" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" t="s">
+        <v>25</v>
+      </c>
+      <c r="F79" t="s">
+        <v>25</v>
+      </c>
+      <c r="G79" t="s">
+        <v>25</v>
+      </c>
+      <c r="H79" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79" t="s">
+        <v>25</v>
+      </c>
+      <c r="J79" t="s">
+        <v>25</v>
+      </c>
+      <c r="K79" t="s">
+        <v>165</v>
+      </c>
+      <c r="L79" t="s">
+        <v>39</v>
+      </c>
+      <c r="M79" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>166</v>
+      </c>
+      <c r="B80" t="s">
+        <v>167</v>
+      </c>
+      <c r="C80" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80" t="s">
+        <v>17</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" t="s">
+        <v>20</v>
+      </c>
+      <c r="I80" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s">
+        <v>42</v>
+      </c>
+      <c r="K80" t="s">
+        <v>60</v>
+      </c>
+      <c r="L80" t="s">
+        <v>43</v>
+      </c>
+      <c r="M80" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>25</v>
+      </c>
+      <c r="B81" t="s">
+        <v>25</v>
+      </c>
+      <c r="C81" t="s">
+        <v>25</v>
+      </c>
+      <c r="D81" t="s">
+        <v>25</v>
+      </c>
+      <c r="E81" t="s">
+        <v>25</v>
+      </c>
+      <c r="F81" t="s">
+        <v>25</v>
+      </c>
+      <c r="G81" t="s">
+        <v>25</v>
+      </c>
+      <c r="H81" t="s">
+        <v>25</v>
+      </c>
+      <c r="I81" t="s">
+        <v>25</v>
+      </c>
+      <c r="J81" t="s">
+        <v>25</v>
+      </c>
+      <c r="K81" t="s">
+        <v>168</v>
+      </c>
+      <c r="L81" t="s">
+        <v>169</v>
+      </c>
+      <c r="M81" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>25</v>
+      </c>
+      <c r="B82" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" t="s">
+        <v>25</v>
+      </c>
+      <c r="D82" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82" t="s">
+        <v>25</v>
+      </c>
+      <c r="G82" t="s">
+        <v>25</v>
+      </c>
+      <c r="H82" t="s">
+        <v>25</v>
+      </c>
+      <c r="I82" t="s">
+        <v>25</v>
+      </c>
+      <c r="J82" t="s">
+        <v>25</v>
+      </c>
+      <c r="K82" t="s">
+        <v>170</v>
+      </c>
+      <c r="L82" t="s">
+        <v>171</v>
+      </c>
+      <c r="M82" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" t="s">
+        <v>25</v>
+      </c>
+      <c r="C83" t="s">
+        <v>25</v>
+      </c>
+      <c r="D83" t="s">
+        <v>25</v>
+      </c>
+      <c r="E83" t="s">
+        <v>25</v>
+      </c>
+      <c r="F83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G83" t="s">
+        <v>25</v>
+      </c>
+      <c r="H83" t="s">
+        <v>25</v>
+      </c>
+      <c r="I83" t="s">
+        <v>25</v>
+      </c>
+      <c r="J83" t="s">
+        <v>25</v>
+      </c>
+      <c r="K83" t="s">
+        <v>172</v>
+      </c>
+      <c r="L83" t="s">
+        <v>173</v>
+      </c>
+      <c r="M83" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>174</v>
+      </c>
+      <c r="B84" t="s">
+        <v>175</v>
+      </c>
+      <c r="C84" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" t="s">
+        <v>17</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" t="s">
+        <v>20</v>
+      </c>
+      <c r="I84" t="s">
+        <v>21</v>
+      </c>
+      <c r="J84" t="s">
+        <v>42</v>
+      </c>
+      <c r="K84" t="s">
+        <v>60</v>
+      </c>
+      <c r="L84" t="s">
+        <v>43</v>
+      </c>
+      <c r="M84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>25</v>
+      </c>
+      <c r="B85" t="s">
+        <v>25</v>
+      </c>
+      <c r="C85" t="s">
+        <v>25</v>
+      </c>
+      <c r="D85" t="s">
+        <v>25</v>
+      </c>
+      <c r="E85" t="s">
+        <v>25</v>
+      </c>
+      <c r="F85" t="s">
+        <v>25</v>
+      </c>
+      <c r="G85" t="s">
+        <v>25</v>
+      </c>
+      <c r="H85" t="s">
+        <v>25</v>
+      </c>
+      <c r="I85" t="s">
+        <v>25</v>
+      </c>
+      <c r="J85" t="s">
+        <v>25</v>
+      </c>
+      <c r="K85" t="s">
+        <v>176</v>
+      </c>
+      <c r="L85" t="s">
+        <v>158</v>
+      </c>
+      <c r="M85" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B86" t="s">
+        <v>25</v>
+      </c>
+      <c r="C86" t="s">
+        <v>25</v>
+      </c>
+      <c r="D86" t="s">
+        <v>25</v>
+      </c>
+      <c r="E86" t="s">
+        <v>25</v>
+      </c>
+      <c r="F86" t="s">
+        <v>25</v>
+      </c>
+      <c r="G86" t="s">
+        <v>25</v>
+      </c>
+      <c r="H86" t="s">
+        <v>25</v>
+      </c>
+      <c r="I86" t="s">
+        <v>25</v>
+      </c>
+      <c r="J86" t="s">
+        <v>25</v>
+      </c>
+      <c r="K86" t="s">
+        <v>177</v>
+      </c>
+      <c r="L86" t="s">
+        <v>178</v>
+      </c>
+      <c r="M86" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" t="s">
+        <v>25</v>
+      </c>
+      <c r="C87" t="s">
+        <v>25</v>
+      </c>
+      <c r="D87" t="s">
+        <v>25</v>
+      </c>
+      <c r="E87" t="s">
+        <v>25</v>
+      </c>
+      <c r="F87" t="s">
+        <v>25</v>
+      </c>
+      <c r="G87" t="s">
+        <v>25</v>
+      </c>
+      <c r="H87" t="s">
+        <v>25</v>
+      </c>
+      <c r="I87" t="s">
+        <v>25</v>
+      </c>
+      <c r="J87" t="s">
+        <v>25</v>
+      </c>
+      <c r="K87" t="s">
+        <v>161</v>
+      </c>
+      <c r="L87" t="s">
+        <v>54</v>
+      </c>
+      <c r="M87" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88" t="s">
+        <v>25</v>
+      </c>
+      <c r="D88" t="s">
+        <v>25</v>
+      </c>
+      <c r="E88" t="s">
+        <v>25</v>
+      </c>
+      <c r="F88" t="s">
+        <v>25</v>
+      </c>
+      <c r="G88" t="s">
+        <v>25</v>
+      </c>
+      <c r="H88" t="s">
+        <v>25</v>
+      </c>
+      <c r="I88" t="s">
+        <v>25</v>
+      </c>
+      <c r="J88" t="s">
+        <v>25</v>
+      </c>
+      <c r="K88" t="s">
+        <v>179</v>
+      </c>
+      <c r="L88" t="s">
+        <v>180</v>
+      </c>
+      <c r="M88" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89" t="s">
+        <v>25</v>
+      </c>
+      <c r="D89" t="s">
+        <v>25</v>
+      </c>
+      <c r="E89" t="s">
+        <v>25</v>
+      </c>
+      <c r="F89" t="s">
+        <v>25</v>
+      </c>
+      <c r="G89" t="s">
+        <v>25</v>
+      </c>
+      <c r="H89" t="s">
+        <v>25</v>
+      </c>
+      <c r="I89" t="s">
+        <v>25</v>
+      </c>
+      <c r="J89" t="s">
+        <v>25</v>
+      </c>
+      <c r="K89" t="s">
+        <v>181</v>
+      </c>
+      <c r="L89" t="s">
+        <v>182</v>
+      </c>
+      <c r="M89" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>183</v>
+      </c>
+      <c r="B90" t="s">
+        <v>184</v>
+      </c>
+      <c r="C90" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" t="s">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s">
+        <v>42</v>
+      </c>
+      <c r="K90" t="s">
+        <v>60</v>
+      </c>
+      <c r="L90" t="s">
+        <v>43</v>
+      </c>
+      <c r="M90" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" t="s">
+        <v>25</v>
+      </c>
+      <c r="C91" t="s">
+        <v>25</v>
+      </c>
+      <c r="D91" t="s">
+        <v>25</v>
+      </c>
+      <c r="E91" t="s">
+        <v>25</v>
+      </c>
+      <c r="F91" t="s">
+        <v>25</v>
+      </c>
+      <c r="G91" t="s">
+        <v>25</v>
+      </c>
+      <c r="H91" t="s">
+        <v>25</v>
+      </c>
+      <c r="I91" t="s">
+        <v>25</v>
+      </c>
+      <c r="J91" t="s">
+        <v>25</v>
+      </c>
+      <c r="K91" t="s">
+        <v>185</v>
+      </c>
+      <c r="L91" t="s">
+        <v>186</v>
+      </c>
+      <c r="M91" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>25</v>
+      </c>
+      <c r="B92" t="s">
+        <v>25</v>
+      </c>
+      <c r="C92" t="s">
+        <v>25</v>
+      </c>
+      <c r="D92" t="s">
+        <v>25</v>
+      </c>
+      <c r="E92" t="s">
+        <v>25</v>
+      </c>
+      <c r="F92" t="s">
+        <v>25</v>
+      </c>
+      <c r="G92" t="s">
+        <v>25</v>
+      </c>
+      <c r="H92" t="s">
+        <v>25</v>
+      </c>
+      <c r="I92" t="s">
+        <v>25</v>
+      </c>
+      <c r="J92" t="s">
+        <v>25</v>
+      </c>
+      <c r="K92" t="s">
+        <v>187</v>
+      </c>
+      <c r="L92" t="s">
+        <v>188</v>
+      </c>
+      <c r="M92" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>189</v>
+      </c>
+      <c r="B93" t="s">
+        <v>190</v>
+      </c>
+      <c r="C93" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" t="s">
+        <v>17</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" t="s">
+        <v>20</v>
+      </c>
+      <c r="I93" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s">
+        <v>42</v>
+      </c>
+      <c r="K93" t="s">
+        <v>60</v>
+      </c>
+      <c r="L93" t="s">
+        <v>43</v>
+      </c>
+      <c r="M93" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>25</v>
+      </c>
+      <c r="B94" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94" t="s">
+        <v>25</v>
+      </c>
+      <c r="D94" t="s">
+        <v>25</v>
+      </c>
+      <c r="E94" t="s">
+        <v>25</v>
+      </c>
+      <c r="F94" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" t="s">
+        <v>25</v>
+      </c>
+      <c r="H94" t="s">
+        <v>25</v>
+      </c>
+      <c r="I94" t="s">
+        <v>25</v>
+      </c>
+      <c r="J94" t="s">
+        <v>25</v>
+      </c>
+      <c r="K94" t="s">
+        <v>191</v>
+      </c>
+      <c r="L94" t="s">
+        <v>192</v>
+      </c>
+      <c r="M94" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>25</v>
+      </c>
+      <c r="B95" t="s">
+        <v>25</v>
+      </c>
+      <c r="C95" t="s">
+        <v>25</v>
+      </c>
+      <c r="D95" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" t="s">
+        <v>25</v>
+      </c>
+      <c r="F95" t="s">
+        <v>25</v>
+      </c>
+      <c r="G95" t="s">
+        <v>25</v>
+      </c>
+      <c r="H95" t="s">
+        <v>25</v>
+      </c>
+      <c r="I95" t="s">
+        <v>25</v>
+      </c>
+      <c r="J95" t="s">
+        <v>25</v>
+      </c>
+      <c r="K95" t="s">
+        <v>193</v>
+      </c>
+      <c r="L95" t="s">
+        <v>194</v>
+      </c>
+      <c r="M95" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>195</v>
+      </c>
+      <c r="B96" t="s">
+        <v>196</v>
+      </c>
+      <c r="C96" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" t="s">
+        <v>17</v>
+      </c>
+      <c r="F96" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" t="s">
+        <v>20</v>
+      </c>
+      <c r="I96" t="s">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s">
+        <v>197</v>
+      </c>
+      <c r="K96" t="s">
+        <v>60</v>
+      </c>
+      <c r="L96" t="s">
+        <v>198</v>
+      </c>
+      <c r="M96" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>25</v>
+      </c>
+      <c r="B97" t="s">
+        <v>25</v>
+      </c>
+      <c r="C97" t="s">
+        <v>25</v>
+      </c>
+      <c r="D97" t="s">
+        <v>25</v>
+      </c>
+      <c r="E97" t="s">
+        <v>25</v>
+      </c>
+      <c r="F97" t="s">
+        <v>25</v>
+      </c>
+      <c r="G97" t="s">
+        <v>25</v>
+      </c>
+      <c r="H97" t="s">
+        <v>25</v>
+      </c>
+      <c r="I97" t="s">
+        <v>25</v>
+      </c>
+      <c r="J97" t="s">
+        <v>25</v>
+      </c>
+      <c r="K97" t="s">
+        <v>199</v>
+      </c>
+      <c r="L97" t="s">
+        <v>200</v>
+      </c>
+      <c r="M97" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>201</v>
+      </c>
+      <c r="B98" t="s">
+        <v>202</v>
+      </c>
+      <c r="C98" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" t="s">
+        <v>17</v>
+      </c>
+      <c r="F98" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" t="s">
+        <v>20</v>
+      </c>
+      <c r="I98" t="s">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s">
+        <v>139</v>
+      </c>
+      <c r="K98" t="s">
+        <v>60</v>
+      </c>
+      <c r="L98" t="s">
+        <v>140</v>
+      </c>
+      <c r="M98" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99" t="s">
+        <v>25</v>
+      </c>
+      <c r="D99" t="s">
+        <v>25</v>
+      </c>
+      <c r="E99" t="s">
+        <v>25</v>
+      </c>
+      <c r="F99" t="s">
+        <v>25</v>
+      </c>
+      <c r="G99" t="s">
+        <v>25</v>
+      </c>
+      <c r="H99" t="s">
+        <v>25</v>
+      </c>
+      <c r="I99" t="s">
+        <v>25</v>
+      </c>
+      <c r="J99" t="s">
+        <v>25</v>
+      </c>
+      <c r="K99" t="s">
+        <v>141</v>
+      </c>
+      <c r="L99" t="s">
+        <v>203</v>
+      </c>
+      <c r="M99" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>25</v>
+      </c>
+      <c r="B100" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100" t="s">
+        <v>25</v>
+      </c>
+      <c r="D100" t="s">
+        <v>25</v>
+      </c>
+      <c r="E100" t="s">
+        <v>25</v>
+      </c>
+      <c r="F100" t="s">
+        <v>25</v>
+      </c>
+      <c r="G100" t="s">
+        <v>25</v>
+      </c>
+      <c r="H100" t="s">
+        <v>25</v>
+      </c>
+      <c r="I100" t="s">
+        <v>25</v>
+      </c>
+      <c r="J100" t="s">
+        <v>25</v>
+      </c>
+      <c r="K100" t="s">
+        <v>135</v>
+      </c>
+      <c r="L100" t="s">
+        <v>136</v>
+      </c>
+      <c r="M100" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>204</v>
+      </c>
+      <c r="B101" t="s">
+        <v>205</v>
+      </c>
+      <c r="C101" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" t="s">
+        <v>20</v>
+      </c>
+      <c r="I101" t="s">
+        <v>21</v>
+      </c>
+      <c r="J101" t="s">
+        <v>42</v>
+      </c>
+      <c r="K101" t="s">
+        <v>60</v>
+      </c>
+      <c r="L101" t="s">
+        <v>43</v>
+      </c>
+      <c r="M101" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>25</v>
+      </c>
+      <c r="B102" t="s">
+        <v>25</v>
+      </c>
+      <c r="C102" t="s">
+        <v>25</v>
+      </c>
+      <c r="D102" t="s">
+        <v>25</v>
+      </c>
+      <c r="E102" t="s">
+        <v>25</v>
+      </c>
+      <c r="F102" t="s">
+        <v>25</v>
+      </c>
+      <c r="G102" t="s">
+        <v>25</v>
+      </c>
+      <c r="H102" t="s">
+        <v>25</v>
+      </c>
+      <c r="I102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J102" t="s">
+        <v>25</v>
+      </c>
+      <c r="K102" t="s">
+        <v>206</v>
+      </c>
+      <c r="L102" t="s">
+        <v>207</v>
+      </c>
+      <c r="M102" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>208</v>
+      </c>
+      <c r="B103" t="s">
+        <v>209</v>
+      </c>
+      <c r="C103" t="s">
+        <v>15</v>
+      </c>
+      <c r="D103" t="s">
+        <v>16</v>
+      </c>
+      <c r="E103" t="s">
+        <v>210</v>
+      </c>
+      <c r="F103" t="s">
+        <v>18</v>
+      </c>
+      <c r="G103" t="s">
+        <v>19</v>
+      </c>
+      <c r="H103" t="s">
+        <v>20</v>
+      </c>
+      <c r="I103" t="s">
+        <v>21</v>
+      </c>
+      <c r="J103" t="s">
+        <v>42</v>
+      </c>
+      <c r="K103" t="s">
+        <v>60</v>
+      </c>
+      <c r="L103" t="s">
+        <v>43</v>
+      </c>
+      <c r="M103" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B104" t="s">
+        <v>25</v>
+      </c>
+      <c r="C104" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104" t="s">
+        <v>25</v>
+      </c>
+      <c r="E104" t="s">
+        <v>25</v>
+      </c>
+      <c r="F104" t="s">
+        <v>25</v>
+      </c>
+      <c r="G104" t="s">
+        <v>25</v>
+      </c>
+      <c r="H104" t="s">
+        <v>25</v>
+      </c>
+      <c r="I104" t="s">
+        <v>25</v>
+      </c>
+      <c r="J104" t="s">
+        <v>25</v>
+      </c>
+      <c r="K104" t="s">
+        <v>211</v>
+      </c>
+      <c r="L104" t="s">
+        <v>212</v>
+      </c>
+      <c r="M104" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>25</v>
+      </c>
+      <c r="B105" t="s">
+        <v>25</v>
+      </c>
+      <c r="C105" t="s">
+        <v>25</v>
+      </c>
+      <c r="D105" t="s">
+        <v>25</v>
+      </c>
+      <c r="E105" t="s">
+        <v>25</v>
+      </c>
+      <c r="F105" t="s">
+        <v>25</v>
+      </c>
+      <c r="G105" t="s">
+        <v>25</v>
+      </c>
+      <c r="H105" t="s">
+        <v>25</v>
+      </c>
+      <c r="I105" t="s">
+        <v>25</v>
+      </c>
+      <c r="J105" t="s">
+        <v>25</v>
+      </c>
+      <c r="K105" t="s">
+        <v>213</v>
+      </c>
+      <c r="L105" t="s">
+        <v>214</v>
+      </c>
+      <c r="M105" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B106" t="s">
+        <v>25</v>
+      </c>
+      <c r="C106" t="s">
+        <v>25</v>
+      </c>
+      <c r="D106" t="s">
+        <v>25</v>
+      </c>
+      <c r="E106" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106" t="s">
+        <v>25</v>
+      </c>
+      <c r="G106" t="s">
+        <v>25</v>
+      </c>
+      <c r="H106" t="s">
+        <v>25</v>
+      </c>
+      <c r="I106" t="s">
+        <v>25</v>
+      </c>
+      <c r="J106" t="s">
+        <v>25</v>
+      </c>
+      <c r="K106" t="s">
+        <v>215</v>
+      </c>
+      <c r="L106" t="s">
+        <v>216</v>
+      </c>
+      <c r="M106" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>217</v>
+      </c>
+      <c r="B107" t="s">
+        <v>218</v>
+      </c>
+      <c r="C107" t="s">
+        <v>15</v>
+      </c>
+      <c r="D107" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" t="s">
+        <v>17</v>
+      </c>
+      <c r="F107" t="s">
+        <v>18</v>
+      </c>
+      <c r="G107" t="s">
+        <v>19</v>
+      </c>
+      <c r="H107" t="s">
+        <v>20</v>
+      </c>
+      <c r="I107" t="s">
+        <v>21</v>
+      </c>
+      <c r="J107" t="s">
+        <v>42</v>
+      </c>
+      <c r="K107" t="s">
+        <v>60</v>
+      </c>
+      <c r="L107" t="s">
+        <v>43</v>
+      </c>
+      <c r="M107" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>25</v>
+      </c>
+      <c r="B108" t="s">
+        <v>25</v>
+      </c>
+      <c r="C108" t="s">
+        <v>25</v>
+      </c>
+      <c r="D108" t="s">
+        <v>25</v>
+      </c>
+      <c r="E108" t="s">
+        <v>25</v>
+      </c>
+      <c r="F108" t="s">
+        <v>25</v>
+      </c>
+      <c r="G108" t="s">
+        <v>25</v>
+      </c>
+      <c r="H108" t="s">
+        <v>25</v>
+      </c>
+      <c r="I108" t="s">
+        <v>25</v>
+      </c>
+      <c r="J108" t="s">
+        <v>25</v>
+      </c>
+      <c r="K108" t="s">
+        <v>219</v>
+      </c>
+      <c r="L108" t="s">
+        <v>162</v>
+      </c>
+      <c r="M108" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>25</v>
+      </c>
+      <c r="B109" t="s">
+        <v>25</v>
+      </c>
+      <c r="C109" t="s">
+        <v>25</v>
+      </c>
+      <c r="D109" t="s">
+        <v>25</v>
+      </c>
+      <c r="E109" t="s">
+        <v>25</v>
+      </c>
+      <c r="F109" t="s">
+        <v>25</v>
+      </c>
+      <c r="G109" t="s">
+        <v>25</v>
+      </c>
+      <c r="H109" t="s">
+        <v>25</v>
+      </c>
+      <c r="I109" t="s">
+        <v>25</v>
+      </c>
+      <c r="J109" t="s">
+        <v>25</v>
+      </c>
+      <c r="K109" t="s">
+        <v>220</v>
+      </c>
+      <c r="L109" t="s">
+        <v>221</v>
+      </c>
+      <c r="M109" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>25</v>
+      </c>
+      <c r="B110" t="s">
+        <v>25</v>
+      </c>
+      <c r="C110" t="s">
+        <v>25</v>
+      </c>
+      <c r="D110" t="s">
+        <v>25</v>
+      </c>
+      <c r="E110" t="s">
+        <v>25</v>
+      </c>
+      <c r="F110" t="s">
+        <v>25</v>
+      </c>
+      <c r="G110" t="s">
+        <v>25</v>
+      </c>
+      <c r="H110" t="s">
+        <v>25</v>
+      </c>
+      <c r="I110" t="s">
+        <v>25</v>
+      </c>
+      <c r="J110" t="s">
+        <v>25</v>
+      </c>
+      <c r="K110" t="s">
+        <v>222</v>
+      </c>
+      <c r="L110" t="s">
+        <v>223</v>
+      </c>
+      <c r="M110" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>25</v>
+      </c>
+      <c r="B111" t="s">
+        <v>25</v>
+      </c>
+      <c r="C111" t="s">
+        <v>25</v>
+      </c>
+      <c r="D111" t="s">
+        <v>25</v>
+      </c>
+      <c r="E111" t="s">
+        <v>25</v>
+      </c>
+      <c r="F111" t="s">
+        <v>25</v>
+      </c>
+      <c r="G111" t="s">
+        <v>25</v>
+      </c>
+      <c r="H111" t="s">
+        <v>25</v>
+      </c>
+      <c r="I111" t="s">
+        <v>25</v>
+      </c>
+      <c r="J111" t="s">
+        <v>25</v>
+      </c>
+      <c r="K111" t="s">
+        <v>224</v>
+      </c>
+      <c r="L111" t="s">
+        <v>47</v>
+      </c>
+      <c r="M111" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -2327,7 +5719,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -698,7 +698,7 @@
     <t>SUMMARY</t>
   </si>
   <si>
-    <t>service_charge_basic_info</t>
+    <t>Service Charge — Basic Information</t>
   </si>
   <si>
     <t>Automated: 30 / Pending: 0</t>
@@ -710,7 +710,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>216e3ef472e1d1a5fd8bdc823b2299e2983f8e64bb024549c10be824c756f7bc</t>
+    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -710,7 +710,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>f9d696e3767564ce556785ab32c8d4d620422045a781f574890b1a82aec41d64</t>
+    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -710,7 +710,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
+    <t>e654a4f812c4ac1bbbd49bec0a6a66cc601c73fe4374e6e441effe43a9071f32</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -710,7 +710,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
+    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -710,7 +710,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
+    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -710,7 +710,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
+    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -710,7 +710,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
+    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -710,7 +710,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
+    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -710,7 +710,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
+    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -710,7 +710,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
+    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -710,7 +710,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
+    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-basic-information.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="service_charge_basic_info" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="230">
   <si>
     <t>TC ID</t>
   </si>
@@ -708,9 +707,6 @@
   </si>
   <si>
     <t>Last Updated: 2026-08-18</t>
-  </si>
-  <si>
-    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>
@@ -5710,20 +5706,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>